--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/audit/mapping_support_migration/source_data/D4_mapping_support_migration_figure_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/audit/mapping_support_migration/source_data/D4_mapping_support_migration_figure_source_data.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,34 +470,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5047</v>
+        <v>4872</v>
       </c>
       <c r="D2" t="n">
-        <v>5046</v>
+        <v>4872</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9653259361997226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>insufficient</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3720</v>
+        <v>175</v>
       </c>
       <c r="D3" t="n">
-        <v>3595</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.03467406380027739</v>
       </c>
     </row>
     <row r="4">
@@ -508,44 +508,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1320</v>
+        <v>1862</v>
       </c>
       <c r="D4" t="n">
-        <v>1284</v>
+        <v>1862</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.3694444444444445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>insufficient</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2976</v>
+        <v>203</v>
       </c>
       <c r="D5" t="n">
-        <v>2976</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.04027777777777778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -554,19 +554,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2232</v>
+        <v>2975</v>
       </c>
       <c r="D6" t="n">
-        <v>2232</v>
+        <v>2975</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5902777777777778</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2880</v>
+        <v>2723</v>
       </c>
       <c r="D7" t="n">
-        <v>2880</v>
+        <v>2723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5228494623655914</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -596,19 +596,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2160</v>
+        <v>2485</v>
       </c>
       <c r="D8" t="n">
-        <v>2160</v>
+        <v>2485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4771505376344086</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2976</v>
+        <v>5040</v>
       </c>
       <c r="D9" t="n">
-        <v>2976</v>
+        <v>5040</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -634,17 +634,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2232</v>
+        <v>5208</v>
       </c>
       <c r="D10" t="n">
-        <v>2232</v>
+        <v>5208</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2976</v>
+        <v>4977</v>
       </c>
       <c r="D11" t="n">
-        <v>2856</v>
+        <v>4977</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.9556451612903226</v>
       </c>
     </row>
     <row r="12">
@@ -676,17 +676,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>insufficient</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2232</v>
+        <v>231</v>
       </c>
       <c r="D12" t="n">
-        <v>2142</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.04435483870967742</v>
       </c>
     </row>
     <row r="13">
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2688</v>
+        <v>4704</v>
       </c>
       <c r="D13" t="n">
-        <v>2688</v>
+        <v>4704</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>5208</v>
       </c>
       <c r="D14" t="n">
-        <v>2016</v>
+        <v>5208</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -743,97 +743,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2976</v>
+        <v>2135</v>
       </c>
       <c r="D15" t="n">
-        <v>2900</v>
+        <v>2135</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.9775641025641025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>insufficient</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2232</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>2232</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1224</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1224</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.5604395604395604</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>insufficient</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>42</v>
-      </c>
-      <c r="D18" t="n">
-        <v>14</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.01923076923076923</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>variable_fallback</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>918</v>
-      </c>
-      <c r="D19" t="n">
-        <v>918</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4203296703296703</v>
+        <v>0.02243589743589744</v>
       </c>
     </row>
   </sheetData>
@@ -847,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,13 +826,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19903</v>
+        <v>23506</v>
       </c>
       <c r="D2" t="n">
-        <v>19657</v>
+        <v>23506</v>
       </c>
       <c r="E2" t="n">
-        <v>0.672967032967033</v>
+        <v>0.794792899408284</v>
       </c>
     </row>
     <row r="3">
@@ -906,38 +843,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>insufficient</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9672</v>
+        <v>609</v>
       </c>
       <c r="D3" t="n">
-        <v>9546</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.327032967032967</v>
+        <v>0.02059171597633136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>embargo</t>
+          <t>development</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>variable_fallback</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>672</v>
+        <v>5460</v>
       </c>
       <c r="D4" t="n">
-        <v>672</v>
+        <v>5460</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1846153846153846</v>
       </c>
     </row>
     <row r="5">
@@ -948,17 +885,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>504</v>
+        <v>1176</v>
       </c>
       <c r="D5" t="n">
-        <v>504</v>
+        <v>1176</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -973,13 +910,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6888</v>
+        <v>12047</v>
       </c>
       <c r="D6" t="n">
-        <v>6812</v>
+        <v>12047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.9959490740740741</v>
       </c>
     </row>
     <row r="7">
@@ -994,34 +931,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003472222222222222</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>internal_validation</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>variable_fallback</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5166</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5166</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.004050925925925926</v>
       </c>
     </row>
   </sheetData>
@@ -1035,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,22 +1018,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16687</v>
+        <v>13432</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>3.275</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7125</v>
+        <v>2.05</v>
       </c>
       <c r="H2" t="n">
         <v>4.6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3574039671600647</v>
+        <v>0.2313877307921382</v>
       </c>
     </row>
     <row r="3">
@@ -1128,31 +1044,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>variable_fallback</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2970</v>
+        <v>3120</v>
       </c>
       <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
         <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.25</v>
       </c>
       <c r="G3" t="n">
         <v>1.675</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4125</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3757575757575757</v>
+        <v>0.4919871794871795</v>
       </c>
     </row>
     <row r="4">
@@ -1168,61 +1084,61 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9546</v>
+        <v>10074</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1625</v>
+        <v>3.675</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5625</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4455269222711083</v>
+        <v>0.2210641254715108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>embargo</t>
+          <t>development</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ORP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>variable_fallback</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>672</v>
+        <v>2340</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3.975</v>
+        <v>3.4625</v>
       </c>
       <c r="G5" t="n">
-        <v>2.675</v>
+        <v>2.29875</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1651785714285714</v>
+        <v>0.252991452991453</v>
       </c>
     </row>
     <row r="6">
@@ -1233,42 +1149,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ORP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>504</v>
+        <v>672</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0125</v>
+        <v>4.012499999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.793125</v>
+        <v>2.8625</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.0744047619047619</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>internal_validation</t>
+          <t>embargo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1277,22 +1193,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6812</v>
+        <v>504</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2.125</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.449999999999999</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3172342924251321</v>
+        <v>0.2400793650793651</v>
       </c>
     </row>
     <row r="8">
@@ -1308,26 +1224,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>6884</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2875</v>
+        <v>3.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3875</v>
+        <v>2.4625</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6125</v>
+        <v>4.449999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.25</v>
+        <v>0.2210923881464265</v>
       </c>
     </row>
     <row r="9">
@@ -1343,61 +1259,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5163</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>2.975</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>2.875</v>
+        <v>1.9375</v>
       </c>
       <c r="H9" t="n">
-        <v>4.487500000000001</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>internal_validation</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>variable_fallback</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>5166</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.4875</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.5625</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.199999999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.6697638404955478</v>
+        <v>0.3912453999612628</v>
       </c>
     </row>
   </sheetData>
@@ -1411,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,16 +1349,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>519</v>
+        <v>324</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>44.09999999999997</v>
+        <v>53.24999999999983</v>
       </c>
       <c r="G2" t="n">
-        <v>273</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
@@ -1488,25 +1369,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>variable_fallback</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>60.59999999999997</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>104</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4">
@@ -1522,49 +1403,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>312</v>
+        <v>245</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>322</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>embargo</t>
+          <t>development</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ORP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>variable_fallback</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>21.79999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="G5" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -1575,36 +1456,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ORP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>variable_fallback</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>41.6999999999999</v>
+        <v>13.59999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>internal_validation</t>
+          <t>embargo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1613,16 +1494,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>234</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>36.34999999999999</v>
+        <v>27.29999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -1638,20 +1519,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>29.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
@@ -1667,49 +1548,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>insufficient</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>47.09999999999997</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>internal_validation</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>variable_fallback</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>117</v>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>103.7999999999998</v>
-      </c>
-      <c r="G10" t="n">
-        <v>585</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
